--- a/Durability I-V figure/tafel plot alt/Overpotential DATA raw alt/O2/75K/Edited/CN BM o2_edited.xlsx
+++ b/Durability I-V figure/tafel plot alt/Overpotential DATA raw alt/O2/75K/Edited/CN BM o2_edited.xlsx
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.55</v>
+        <v>-0.5621</v>
       </c>
     </row>
     <row r="5">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.0445</v>
+        <v>-0.0495</v>
       </c>
       <c r="V5" s="0" t="inlineStr">
         <is>
